--- a/abastecimentos_092026.xlsx
+++ b/abastecimentos_092026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="221">
   <si>
     <t>DATA</t>
   </si>
@@ -430,6 +430,267 @@
   </si>
   <si>
     <t>ELUANE ANGELICA TONZAR DE LIMA</t>
+  </si>
+  <si>
+    <t>AVC8J76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENNER DOS SANTOS </t>
+  </si>
+  <si>
+    <t>AZS0C95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINCOLN FRANCEL PIMENTA </t>
+  </si>
+  <si>
+    <t>QNK9D75</t>
+  </si>
+  <si>
+    <t>REGINALDO MENDES OLIVEIRA</t>
+  </si>
+  <si>
+    <t>QNP1A41</t>
+  </si>
+  <si>
+    <t>APARECIDO JOEL SANT ANA</t>
+  </si>
+  <si>
+    <t>QNK9D78</t>
+  </si>
+  <si>
+    <t>NILTON DE JESUS RODRIGUES DE SOUZA</t>
+  </si>
+  <si>
+    <t>QQK0B48</t>
+  </si>
+  <si>
+    <t>GEDIVALDO SOUZA LUZ ALVES</t>
+  </si>
+  <si>
+    <t>SDX2B62</t>
+  </si>
+  <si>
+    <t>DANILO CASSIANO FERREIRA</t>
+  </si>
+  <si>
+    <t>SDX2F46</t>
+  </si>
+  <si>
+    <t>NILSON RODRIGUES DE SOUZA</t>
+  </si>
+  <si>
+    <t>SDX2F47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS ENRIQUE DA SILVA LUIZ </t>
+  </si>
+  <si>
+    <t>SDX2G15</t>
+  </si>
+  <si>
+    <t>ODAIR GONCALVES MIRANDA</t>
+  </si>
+  <si>
+    <t>SEP5B09</t>
+  </si>
+  <si>
+    <t>JONAS GOGOLA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>TBF0D34</t>
+  </si>
+  <si>
+    <t>CLAUDIO JOSE KREGENSKI</t>
+  </si>
+  <si>
+    <t>TBF1H99</t>
+  </si>
+  <si>
+    <t>JOAO PAULO LISNIOWSKI</t>
+  </si>
+  <si>
+    <t>SFA2J39</t>
+  </si>
+  <si>
+    <t>AUTO POSTO NOVA AMIZADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE AUGUSTO DOS SANTOS </t>
+  </si>
+  <si>
+    <t>QMX6B92</t>
+  </si>
+  <si>
+    <t>POSTO MARAJO CUIABA</t>
+  </si>
+  <si>
+    <t>EVERTON TEODORO DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>FILIAL VARZEA GRANDE - 0009-75</t>
+  </si>
+  <si>
+    <t>BCJ7I75</t>
+  </si>
+  <si>
+    <t>POSTO ITAIPAVA</t>
+  </si>
+  <si>
+    <t>SILVANO DA SILVA FREITAS</t>
+  </si>
+  <si>
+    <t>FILIAL ITAJAI - 0011-90</t>
+  </si>
+  <si>
+    <t>AZS0D29</t>
+  </si>
+  <si>
+    <t>PAULO CESAR VICENTINI</t>
+  </si>
+  <si>
+    <t>QNP1A57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDINEY FERREIRA PRIMO </t>
+  </si>
+  <si>
+    <t>QOU-0500</t>
+  </si>
+  <si>
+    <t>WILLIAM ANDRADE DE MOURA</t>
+  </si>
+  <si>
+    <t>SES9A69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIAN FABIANO LUIZ DA SILVA </t>
+  </si>
+  <si>
+    <t>TBA5F80</t>
+  </si>
+  <si>
+    <t>ANTONIO ROBERTO BELTRAMINI</t>
+  </si>
+  <si>
+    <t>AZS0D19</t>
+  </si>
+  <si>
+    <t>POSTO INTERNO - BASE CAMPO GRANDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE TELES DA CRUZ </t>
+  </si>
+  <si>
+    <t>FILIAL CAMPO GRANDE - 0022-42</t>
+  </si>
+  <si>
+    <t>BAD6E28</t>
+  </si>
+  <si>
+    <t>JHONATAN ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>SDZ6F45</t>
+  </si>
+  <si>
+    <t>DIEGO LAURINDO FURQUIM</t>
+  </si>
+  <si>
+    <t>QNU4G40</t>
+  </si>
+  <si>
+    <t>JOSUE LOPES DE SENE</t>
+  </si>
+  <si>
+    <t>QNU4G44</t>
+  </si>
+  <si>
+    <t>RODRIGO DE SOUZA MACHADO</t>
+  </si>
+  <si>
+    <t>QNU4G46</t>
+  </si>
+  <si>
+    <t>NELSON SOBOTHE</t>
+  </si>
+  <si>
+    <t>SDX2B07</t>
+  </si>
+  <si>
+    <t>CLAUDINEI FRANCISCO FERREIRA</t>
+  </si>
+  <si>
+    <t>SEP5B03</t>
+  </si>
+  <si>
+    <t>LEOMAR MOREIRA</t>
+  </si>
+  <si>
+    <t>TBF0D28</t>
+  </si>
+  <si>
+    <t>VALDECI FERREIRA DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>TBF0D29</t>
+  </si>
+  <si>
+    <t>LIDIOMAR DA SILVA DE SOUZA</t>
+  </si>
+  <si>
+    <t>BBK0D19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TADEU JOSE CAETANO DE SOUZA </t>
+  </si>
+  <si>
+    <t>BCK8A66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO FRANCA DOS SANTOS </t>
+  </si>
+  <si>
+    <t>ARS7C05</t>
+  </si>
+  <si>
+    <t>TBA5F79</t>
+  </si>
+  <si>
+    <t>FABIO CARLOS ARAUJO DO CARMO</t>
+  </si>
+  <si>
+    <t>BAO1D96</t>
+  </si>
+  <si>
+    <t>DIEGO FRANCISCO DE SOUZA</t>
+  </si>
+  <si>
+    <t>SDX2F45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NILSON APARECIDO SAMPAIO </t>
+  </si>
+  <si>
+    <t>QMX6B74</t>
+  </si>
+  <si>
+    <t>RENATO PEREIRA FRANÇA</t>
+  </si>
+  <si>
+    <t>QND1B67</t>
+  </si>
+  <si>
+    <t>POSTO QUELUZ</t>
+  </si>
+  <si>
+    <t>AGUINALDO DOS SANTOS TEIXEIRA</t>
+  </si>
+  <si>
+    <t>TBA5F81</t>
+  </si>
+  <si>
+    <t>EDE WILSON RODRIGUES</t>
   </si>
 </sst>
 </file>
@@ -697,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2457,28 +2718,2087 @@
         <v>46262</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="3">
+        <v>720.22</v>
+      </c>
+      <c r="E61" s="3">
+        <v>138</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="3">
+        <v>586131</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1137.74</v>
+      </c>
+      <c r="E62" s="3">
+        <v>218</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="3">
+        <v>574370</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="3">
+        <v>240.07</v>
+      </c>
+      <c r="E63" s="3">
+        <v>45</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="3">
+        <v>432445</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="3">
+        <v>589.74</v>
+      </c>
+      <c r="E64" s="3">
+        <v>113</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="3">
+        <v>492462</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1038.58</v>
+      </c>
+      <c r="E65" s="3">
+        <v>199</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="3">
+        <v>459498</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1184.71</v>
+      </c>
+      <c r="E66" s="3">
+        <v>227</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="3">
+        <v>510304</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1017.7</v>
+      </c>
+      <c r="E67" s="3">
+        <v>195</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" s="3">
+        <v>686910</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="3">
+        <v>720.22</v>
+      </c>
+      <c r="E68" s="3">
+        <v>138</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="3">
+        <v>473091</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="3">
+        <v>1216.02</v>
+      </c>
+      <c r="E69" s="3">
+        <v>233</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3">
+        <v>134769</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="3">
+        <v>2530.81</v>
+      </c>
+      <c r="E70" s="3">
+        <v>493</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="3">
+        <v>760542</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3">
+        <v>1904.53</v>
+      </c>
+      <c r="E71" s="3">
+        <v>371</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="3">
+        <v>773718</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1498.98</v>
+      </c>
+      <c r="E72" s="3">
+        <v>292</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="3">
+        <v>625767</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="3">
+        <v>1950.73</v>
+      </c>
+      <c r="E73" s="3">
+        <v>380</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="3">
+        <v>284565</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="3">
+        <v>2802.89</v>
+      </c>
+      <c r="E74" s="3">
+        <v>546</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3">
+        <v>257852</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2315.21</v>
+      </c>
+      <c r="E75" s="3">
+        <v>451</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="3">
+        <v>269301</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="3">
+        <v>2053.4</v>
+      </c>
+      <c r="E76" s="3">
+        <v>400</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="3">
+        <v>283087</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="3">
+        <v>2315.21</v>
+      </c>
+      <c r="E77" s="3">
+        <v>451</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="3">
+        <v>230993</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="3">
+        <v>2597.5500000000002</v>
+      </c>
+      <c r="E78" s="3">
+        <v>506</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="3">
+        <v>103240</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="3">
+        <v>2053.4</v>
+      </c>
+      <c r="E79" s="3">
+        <v>400</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="3">
+        <v>95039</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1291.27</v>
+      </c>
+      <c r="E80" s="3">
+        <v>193.01499999999999</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="3">
+        <v>85318</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D81" s="3">
         <v>1384.28</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E81" s="3">
         <v>180.01</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="F81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="3">
         <v>573543</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H81" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D82" s="3">
+        <v>1449.8</v>
+      </c>
+      <c r="E82" s="3">
+        <v>220</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="3">
+        <v>371225</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1477.65</v>
+      </c>
+      <c r="E83" s="3">
+        <v>211.39500000000001</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="3">
+        <v>498240</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="3">
+        <v>758.5</v>
+      </c>
+      <c r="E84" s="3">
+        <v>145.03</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="3">
+        <v>869921</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="3">
+        <v>983.24</v>
+      </c>
+      <c r="E85" s="3">
+        <v>188</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="3">
+        <v>572461</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="3">
+        <v>774.04</v>
+      </c>
+      <c r="E86" s="3">
+        <v>148</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="3">
+        <v>402028</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="3">
+        <v>883.87</v>
+      </c>
+      <c r="E87" s="3">
+        <v>169</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="3">
+        <v>751393</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="3">
+        <v>502.13</v>
+      </c>
+      <c r="E88" s="3">
+        <v>96.01</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="3">
+        <v>686068</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="3">
+        <v>758.35</v>
+      </c>
+      <c r="E89" s="3">
+        <v>145</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="3">
+        <v>604695</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="3">
+        <v>753.12</v>
+      </c>
+      <c r="E90" s="3">
+        <v>144</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="3">
+        <v>414399</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="3">
+        <v>857.72</v>
+      </c>
+      <c r="E91" s="3">
+        <v>164</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="3">
+        <v>156838</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" s="3">
+        <v>2745.75</v>
+      </c>
+      <c r="E92" s="3">
+        <v>525</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="3">
+        <v>93957</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D93" s="3">
+        <v>579.66</v>
+      </c>
+      <c r="E93" s="3">
+        <v>109</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="3">
+        <v>527583</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" s="3">
+        <v>872.15</v>
+      </c>
+      <c r="E94" s="3">
+        <v>164</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3">
+        <v>528260</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="3">
+        <v>668.03</v>
+      </c>
+      <c r="E95" s="3">
+        <v>128</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="3">
+        <v>577366</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="3">
+        <v>782.85</v>
+      </c>
+      <c r="E96" s="3">
+        <v>150</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3">
+        <v>925279</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1394.73</v>
+      </c>
+      <c r="E97" s="3">
+        <v>267</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="3">
+        <v>399630</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="3">
+        <v>994.96</v>
+      </c>
+      <c r="E98" s="3">
+        <v>114</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="3">
+        <v>459723</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="3">
+        <v>156.57</v>
+      </c>
+      <c r="E99" s="3">
+        <v>30</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="3">
+        <v>137250</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="3">
+        <v>1080.33</v>
+      </c>
+      <c r="E100" s="3">
+        <v>207</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3">
+        <v>133195</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="3">
+        <v>1785.43</v>
+      </c>
+      <c r="E101" s="3">
+        <v>351</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="3">
+        <v>735940</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1932.94</v>
+      </c>
+      <c r="E102" s="3">
+        <v>380</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3">
+        <v>748738</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="3">
+        <v>1836.3</v>
+      </c>
+      <c r="E103" s="3">
+        <v>361</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="3">
+        <v>736888</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="3">
+        <v>2472.13</v>
+      </c>
+      <c r="E104" s="3">
+        <v>486</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="3">
+        <v>728995</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" s="3">
+        <v>2441.61</v>
+      </c>
+      <c r="E105" s="3">
+        <v>480</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="3">
+        <v>301390</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="3">
+        <v>1627.74</v>
+      </c>
+      <c r="E106" s="3">
+        <v>320</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="3">
+        <v>225910</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="3">
+        <v>1749.82</v>
+      </c>
+      <c r="E107" s="3">
+        <v>344</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="3">
+        <v>97842</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="3">
+        <v>2136.41</v>
+      </c>
+      <c r="E108" s="3">
+        <v>420</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="3">
+        <v>98355</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="3">
+        <v>2502.65</v>
+      </c>
+      <c r="E109" s="3">
+        <v>492</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="3">
+        <v>98324</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D110" s="3">
+        <v>985.93</v>
+      </c>
+      <c r="E110" s="3">
+        <v>149.61099999999999</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="3">
+        <v>387276</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D111" s="3">
+        <v>1710.94</v>
+      </c>
+      <c r="E111" s="3">
+        <v>272.01</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="3">
+        <v>574207</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D112" s="3">
+        <v>1683.74</v>
+      </c>
+      <c r="E112" s="3">
+        <v>272.01</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="3">
+        <v>574207</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D113" s="3">
+        <v>674.96</v>
+      </c>
+      <c r="E113" s="3">
+        <v>109.04</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="3">
+        <v>564193</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D114" s="3">
+        <v>796.57</v>
+      </c>
+      <c r="E114" s="3">
+        <v>119.07</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="3">
+        <v>758412</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" s="3">
+        <v>678.47</v>
+      </c>
+      <c r="E115" s="3">
+        <v>130</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="3">
+        <v>959320</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" s="3">
+        <v>413.17</v>
+      </c>
+      <c r="E116" s="3">
+        <v>79</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="3">
+        <v>572803</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" s="3">
+        <v>3818</v>
+      </c>
+      <c r="E117" s="3">
+        <v>730.02</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="3">
+        <v>415951</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D118" s="3">
+        <v>3226.91</v>
+      </c>
+      <c r="E118" s="3">
+        <v>617</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="3">
+        <v>91246</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119" s="3">
+        <v>920.48</v>
+      </c>
+      <c r="E119" s="3">
+        <v>176</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119" s="3">
+        <v>38991</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>46263</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120" s="3">
+        <v>1072.04</v>
+      </c>
+      <c r="E120" s="3">
+        <v>204.98</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" s="3">
+        <v>19918</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" s="3">
+        <v>730.66</v>
+      </c>
+      <c r="E121" s="3">
+        <v>140</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" s="3">
+        <v>713521</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" s="3">
+        <v>652.37</v>
+      </c>
+      <c r="E122" s="3">
+        <v>125</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="3">
+        <v>205484</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" s="3">
+        <v>652.37</v>
+      </c>
+      <c r="E123" s="3">
+        <v>125</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="3">
+        <v>687236</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" s="3">
+        <v>1922.77</v>
+      </c>
+      <c r="E124" s="3">
+        <v>378</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="3">
+        <v>749347</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="3">
+        <v>2782.42</v>
+      </c>
+      <c r="E125" s="3">
+        <v>547</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="3">
+        <v>577395</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="3">
+        <v>1627.74</v>
+      </c>
+      <c r="E126" s="3">
+        <v>320</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="3">
+        <v>299530</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="3">
+        <v>3018.49</v>
+      </c>
+      <c r="E127" s="3">
+        <v>588</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="3">
+        <v>263159</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="3">
+        <v>1627.74</v>
+      </c>
+      <c r="E128" s="3">
+        <v>320</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="3">
+        <v>215580</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D129" s="3">
+        <v>2396.25</v>
+      </c>
+      <c r="E129" s="3">
+        <v>375</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="3">
+        <v>411390</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="3">
+        <v>2970.25</v>
+      </c>
+      <c r="E130" s="3">
+        <v>475.24</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="3">
+        <v>441356</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131" s="3">
+        <v>502.08</v>
+      </c>
+      <c r="E131" s="3">
+        <v>96</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131" s="3">
+        <v>729750</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" s="3">
+        <v>3169.38</v>
+      </c>
+      <c r="E132" s="3">
+        <v>606</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G132" s="3">
+        <v>91269</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
